--- a/mard-221-github/colors.xlsx
+++ b/mard-221-github/colors.xlsx
@@ -2489,12 +2489,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>原始查询名</t>
+          <t>系列短名</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>嗜MARD家 / MARD</t>
+          <t>MARD家源码版</t>
         </is>
       </c>
     </row>

--- a/mard-221-github/colors.xlsx
+++ b/mard-221-github/colors.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_A" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_B" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_C" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_D" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_E" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_F" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_G" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_H" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_M" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_A" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_B" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_C" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_D" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05_E" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06_F" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="07_G" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="08_H" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="09_M" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/mard-221-github/colors.xlsx
+++ b/mard-221-github/colors.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_A" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_B" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_C" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_D" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_E" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="06_F" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_G" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_H" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09_M" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_A" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_B" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_C" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_D" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_E" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_F" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_G" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_H" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_M" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
